--- a/Config/Excels/Tables/U-UIConfig-UI配置表.xlsx
+++ b/Config/Excels/Tables/U-UIConfig-UI配置表.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59">
   <si>
     <t>##var</t>
   </si>
@@ -101,7 +101,7 @@
     <t>WinMain</t>
   </si>
   <si>
-    <t>主界面</t>
+    <t>游戏主界面</t>
   </si>
   <si>
     <t>MainUI</t>
@@ -113,7 +113,7 @@
     <t>WinLogin</t>
   </si>
   <si>
-    <t>登录界面</t>
+    <t>游戏登录界面</t>
   </si>
   <si>
     <t>Normal</t>
@@ -122,19 +122,19 @@
     <t>WinPlayerList</t>
   </si>
   <si>
-    <t>角色列表</t>
+    <t>角色列表选择界面</t>
   </si>
   <si>
     <t>WinPlayerCreate</t>
   </si>
   <si>
-    <t>创建角色</t>
+    <t>创建角色界面</t>
   </si>
   <si>
     <t>WinLoginAnnouncement</t>
   </si>
   <si>
-    <t>登录公告</t>
+    <t>登录公告弹窗</t>
   </si>
   <si>
     <t>WinBag</t>
@@ -146,13 +146,16 @@
     <t>WinGlobalLoading</t>
   </si>
   <si>
-    <t>全局Loading</t>
+    <t>全局Loading界面</t>
+  </si>
+  <si>
+    <t>Loading</t>
   </si>
   <si>
     <t>WinDialogMessageBox</t>
   </si>
   <si>
-    <t>弹窗消息框</t>
+    <t>通用消息框弹窗</t>
   </si>
   <si>
     <t>Window</t>
@@ -161,7 +164,7 @@
     <t>WinGlobalMask</t>
   </si>
   <si>
-    <t>全局遮罩</t>
+    <t>全局遮罩界面</t>
   </si>
   <si>
     <t>Guide</t>
@@ -173,19 +176,25 @@
     <t>WinClickGuide</t>
   </si>
   <si>
-    <t>点击引导</t>
+    <t>点击引导界面</t>
   </si>
   <si>
     <t>WinDialogGuide</t>
   </si>
   <si>
-    <t>对话引导</t>
+    <t>对话引导界面</t>
   </si>
   <si>
     <t>WinLoadingScene</t>
   </si>
   <si>
-    <t>Loading场景</t>
+    <t>场景Loading界面</t>
+  </si>
+  <si>
+    <t>WinReconnecting</t>
+  </si>
+  <si>
+    <t>断线重连中界面</t>
   </si>
 </sst>
 </file>
@@ -193,10 +202,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -220,6 +229,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -228,7 +244,76 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -243,61 +328,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -317,47 +350,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -378,13 +387,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -396,163 +561,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -577,6 +586,17 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -606,6 +626,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -623,23 +658,17 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -658,193 +687,174 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="31" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="31" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1166,457 +1176,486 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultColWidth="12" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="12" style="1"/>
+    <col min="1" max="1" width="12" style="1" customWidth="1"/>
     <col min="2" max="2" width="25" style="2" customWidth="1"/>
     <col min="3" max="3" width="15" style="2" customWidth="1"/>
     <col min="4" max="6" width="17" style="1" customWidth="1"/>
     <col min="7" max="7" width="21.5555555555556" style="1" customWidth="1"/>
     <col min="8" max="8" width="17" style="1" customWidth="1"/>
-    <col min="9" max="9" width="20.2222222222222" customWidth="1"/>
+    <col min="9" max="9" width="20.2222222222222" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" ht="40.5" spans="1:9">
-      <c r="A4" s="3" t="s">
+    <row r="4" ht="40.5" customHeight="1" spans="1:9">
+      <c r="A4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="4" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="4"/>
-      <c r="B5" s="5" t="s">
+      <c r="A5" s="5"/>
+      <c r="B5" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="5">
         <v>0.3</v>
       </c>
-      <c r="G5" s="4" t="b">
+      <c r="G5" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="H5" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I5" s="4" t="b">
+      <c r="H5" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="4"/>
-      <c r="B6" s="5" t="s">
+      <c r="A6" s="5"/>
+      <c r="B6" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="5">
         <v>0.3</v>
       </c>
-      <c r="G6" s="4" t="b">
+      <c r="G6" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="H6" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" s="4" t="b">
+      <c r="H6" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="4"/>
-      <c r="B7" s="5" t="s">
+      <c r="A7" s="5"/>
+      <c r="B7" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="5">
         <v>0.3</v>
       </c>
-      <c r="G7" s="4" t="b">
+      <c r="G7" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="H7" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I7" s="4" t="b">
+      <c r="H7" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="4"/>
-      <c r="B8" s="5" t="s">
+      <c r="A8" s="5"/>
+      <c r="B8" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="5">
         <v>0.3</v>
       </c>
-      <c r="G8" s="4" t="b">
+      <c r="G8" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="H8" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I8" s="4" t="b">
+      <c r="H8" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="4"/>
-      <c r="B9" s="5" t="s">
+      <c r="A9" s="5"/>
+      <c r="B9" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="5">
         <v>0.3</v>
       </c>
-      <c r="G9" s="4" t="b">
+      <c r="G9" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="H9" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" s="4" t="b">
+      <c r="H9" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="4"/>
-      <c r="B10" s="5" t="s">
+      <c r="A10" s="5"/>
+      <c r="B10" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="5">
         <v>0.3</v>
       </c>
-      <c r="G10" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H10" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I10" s="4" t="b">
+      <c r="G10" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="4"/>
-      <c r="B11" s="5" t="s">
+      <c r="A11" s="5"/>
+      <c r="B11" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="G11" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="5"/>
+      <c r="B12" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="G12" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="5"/>
+      <c r="B13" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="G13" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="5"/>
+      <c r="B14" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F14" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="G14" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="5"/>
+      <c r="B15" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="G15" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="5"/>
+      <c r="B16" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E16" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F16" s="5">
         <v>0.3</v>
       </c>
-      <c r="G11" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H11" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I11" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="4"/>
-      <c r="B12" s="5" t="s">
+      <c r="G16" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9">
+      <c r="B17" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E12" s="4" t="s">
+      <c r="E17" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F17" s="5">
         <v>0.3</v>
       </c>
-      <c r="G12" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H12" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I12" s="4" t="b">
+      <c r="G17" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="4"/>
-      <c r="B13" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F13" s="4">
-        <v>0.3</v>
-      </c>
-      <c r="G13" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H13" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I13" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="4"/>
-      <c r="B14" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F14" s="4">
-        <v>0.3</v>
-      </c>
-      <c r="G14" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H14" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="4"/>
-      <c r="B15" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F15" s="4">
-        <v>0.3</v>
-      </c>
-      <c r="G15" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H15" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I15" s="4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="4"/>
-      <c r="B16" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F16" s="4">
-        <v>0.3</v>
-      </c>
-      <c r="G16" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H16" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I16" s="4" t="b">
-        <v>0</v>
-      </c>
+    <row r="18" spans="6:6">
+      <c r="F18" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Config/Excels/Tables/U-UIConfig-UI配置表.xlsx
+++ b/Config/Excels/Tables/U-UIConfig-UI配置表.xlsx
@@ -242,17 +242,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -273,6 +264,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
@@ -280,40 +279,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -327,10 +295,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -351,22 +328,45 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -387,49 +387,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -441,127 +555,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -592,11 +592,24 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -616,11 +629,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -640,26 +659,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -672,21 +687,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -695,145 +695,145 @@
     <xf numFmtId="42" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1463,7 +1463,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:9">
